--- a/fall_2025/proposal/gantt/Gantt Chart Senior Design.xlsx
+++ b/fall_2025/proposal/gantt/Gantt Chart Senior Design.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29303"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70362EDE-C065-4DF5-BFFB-1B1D150D1C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9DD4AEF-BDDC-4BDB-9984-CB9156E283DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,12 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
   <si>
     <t>Flight Controls Lab</t>
   </si>
   <si>
-    <t>The Rubber Duckies</t>
+    <t>Flight Controls Team</t>
   </si>
   <si>
     <t>Project start: 8/20/25</t>
@@ -102,24 +102,24 @@
     <t>Decorate Lab Corner</t>
   </si>
   <si>
+    <t>Mathmatical Model</t>
+  </si>
+  <si>
+    <t>Simon &amp; Brady</t>
+  </si>
+  <si>
     <t>Evaluate Finances</t>
   </si>
   <si>
+    <t>Order PCB</t>
+  </si>
+  <si>
     <t>Decide Lab Safety Measures</t>
   </si>
   <si>
     <t>Aydan &amp; Simon</t>
   </si>
   <si>
-    <t>Mathmatical Model</t>
-  </si>
-  <si>
-    <t>Simon &amp; Brady</t>
-  </si>
-  <si>
-    <t>Order PCB</t>
-  </si>
-  <si>
     <t>Battery Storage Solution</t>
   </si>
   <si>
@@ -213,7 +213,7 @@
     <t>Brady &amp; Aydan</t>
   </si>
   <si>
-    <t>Test P1 Design</t>
+    <t>P1 Design Test &amp; Integration</t>
   </si>
   <si>
     <t>Design PCB</t>
@@ -222,7 +222,7 @@
     <t>Prototype 2 Drone Assembly</t>
   </si>
   <si>
-    <t>Test P2 Design</t>
+    <t>P2 Design Test &amp; Integration</t>
   </si>
   <si>
     <t>Lab Design</t>
@@ -259,7 +259,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="ddd\,\ m/d/yyyy"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,8 +462,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="3" tint="0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -581,6 +588,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -816,7 +835,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
@@ -909,7 +928,6 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -935,7 +953,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -957,7 +974,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -983,15 +999,11 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1023,10 +1035,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1039,10 +1049,8 @@
     <xf numFmtId="0" fontId="20" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1070,6 +1078,87 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1428,106 +1517,106 @@
   <sheetData>
     <row r="1" spans="1:40" ht="60">
       <c r="A1" s="41"/>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
-      <c r="Z1" s="59"/>
-      <c r="AA1" s="59"/>
-      <c r="AB1" s="59"/>
-      <c r="AC1" s="59"/>
-      <c r="AD1" s="59"/>
-      <c r="AE1" s="59"/>
-      <c r="AF1" s="59"/>
-      <c r="AG1" s="59"/>
-      <c r="AH1" s="59"/>
-      <c r="AI1" s="59"/>
-      <c r="AJ1" s="59"/>
-      <c r="AK1" s="59"/>
-      <c r="AL1" s="59"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="58"/>
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="58"/>
+      <c r="AC1" s="58"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="58"/>
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="58"/>
+      <c r="AH1" s="58"/>
+      <c r="AI1" s="58"/>
+      <c r="AJ1" s="58"/>
+      <c r="AK1" s="58"/>
+      <c r="AL1" s="58"/>
       <c r="AM1" s="40"/>
     </row>
     <row r="2" spans="1:40" ht="20.25">
-      <c r="A2" s="60"/>
-      <c r="B2" s="69" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="72" t="s">
+      <c r="C2" s="68"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="81" t="s">
+      <c r="F2" s="71"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="81"/>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="81"/>
-      <c r="AB2" s="81"/>
-      <c r="AC2" s="81"/>
-      <c r="AD2" s="82"/>
-      <c r="AE2" s="82"/>
-      <c r="AF2" s="83"/>
-      <c r="AG2" s="83"/>
-      <c r="AH2" s="83"/>
-      <c r="AI2" s="83"/>
-      <c r="AJ2" s="83"/>
-      <c r="AK2" s="83"/>
-      <c r="AL2" s="83"/>
-      <c r="AM2" s="61"/>
+      <c r="V2" s="78"/>
+      <c r="W2" s="78"/>
+      <c r="X2" s="78"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="78"/>
+      <c r="AA2" s="78"/>
+      <c r="AB2" s="78"/>
+      <c r="AC2" s="78"/>
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="79"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="80"/>
+      <c r="AH2" s="80"/>
+      <c r="AI2" s="80"/>
+      <c r="AJ2" s="80"/>
+      <c r="AK2" s="80"/>
+      <c r="AL2" s="146"/>
+      <c r="AM2" s="60"/>
     </row>
     <row r="3" spans="1:40" ht="18">
-      <c r="A3" s="60"/>
-      <c r="B3" s="95" t="s">
+      <c r="A3" s="59"/>
+      <c r="B3" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="96" t="s">
+      <c r="C3" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="97"/>
-      <c r="E3" s="100"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="95"/>
       <c r="F3" s="49"/>
-      <c r="G3" s="102"/>
+      <c r="G3" s="97"/>
       <c r="H3" s="44"/>
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
@@ -1536,7 +1625,7 @@
       <c r="M3" s="45"/>
       <c r="N3" s="45"/>
       <c r="O3" s="45"/>
-      <c r="P3" s="50"/>
+      <c r="P3" s="150"/>
       <c r="Q3" s="45"/>
       <c r="R3" s="45"/>
       <c r="S3" s="45"/>
@@ -1547,7 +1636,7 @@
       <c r="V3" s="46"/>
       <c r="W3" s="46"/>
       <c r="X3" s="46"/>
-      <c r="Y3" s="46"/>
+      <c r="Y3" s="144"/>
       <c r="Z3" s="46"/>
       <c r="AA3" s="46"/>
       <c r="AB3" s="46"/>
@@ -1560,63 +1649,63 @@
       <c r="AI3" s="48"/>
       <c r="AJ3" s="48"/>
       <c r="AK3" s="48"/>
-      <c r="AL3" s="48"/>
-      <c r="AM3" s="61"/>
+      <c r="AL3" s="147"/>
+      <c r="AM3" s="60"/>
     </row>
     <row r="4" spans="1:40" ht="18">
-      <c r="A4" s="60"/>
-      <c r="B4" s="98" t="s">
+      <c r="A4" s="59"/>
+      <c r="B4" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="99" t="s">
+      <c r="C4" s="94" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="67" t="s">
+      <c r="E4" s="96"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="151"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="68"/>
-      <c r="AE4" s="68"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
-      <c r="AM4" s="61"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="145"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="148"/>
+      <c r="AM4" s="60"/>
     </row>
     <row r="5" spans="1:40">
-      <c r="A5" s="60"/>
+      <c r="A5" s="59"/>
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
-      <c r="F5" s="51"/>
+      <c r="F5" s="50"/>
       <c r="G5" s="43" t="s">
         <v>10</v>
       </c>
@@ -1651,10 +1740,10 @@
       <c r="AJ5" s="42"/>
       <c r="AK5" s="42"/>
       <c r="AL5" s="42"/>
-      <c r="AM5" s="61"/>
+      <c r="AM5" s="60"/>
     </row>
     <row r="6" spans="1:40">
-      <c r="A6" s="60"/>
+      <c r="A6" s="59"/>
       <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
@@ -1764,54 +1853,54 @@
       <c r="AL6" s="5">
         <v>32</v>
       </c>
-      <c r="AM6" s="84"/>
+      <c r="AM6" s="81"/>
       <c r="AN6" s="1"/>
     </row>
     <row r="7" spans="1:40">
-      <c r="A7" s="60"/>
+      <c r="A7" s="59"/>
       <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="91"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="91"/>
-      <c r="U7" s="91"/>
-      <c r="V7" s="91"/>
-      <c r="W7" s="91"/>
-      <c r="X7" s="91"/>
-      <c r="Y7" s="91"/>
-      <c r="Z7" s="91"/>
-      <c r="AA7" s="91"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="91"/>
-      <c r="AD7" s="91"/>
-      <c r="AE7" s="91"/>
-      <c r="AF7" s="91"/>
-      <c r="AG7" s="91"/>
-      <c r="AH7" s="91"/>
-      <c r="AI7" s="91"/>
-      <c r="AJ7" s="91"/>
-      <c r="AK7" s="91"/>
-      <c r="AL7" s="91"/>
-      <c r="AM7" s="61"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="88"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="87"/>
+      <c r="P7" s="87"/>
+      <c r="Q7" s="87"/>
+      <c r="R7" s="87"/>
+      <c r="S7" s="87"/>
+      <c r="T7" s="87"/>
+      <c r="U7" s="87"/>
+      <c r="V7" s="87"/>
+      <c r="W7" s="87"/>
+      <c r="X7" s="87"/>
+      <c r="Y7" s="87"/>
+      <c r="Z7" s="87"/>
+      <c r="AA7" s="87"/>
+      <c r="AB7" s="87"/>
+      <c r="AC7" s="87"/>
+      <c r="AD7" s="87"/>
+      <c r="AE7" s="87"/>
+      <c r="AF7" s="87"/>
+      <c r="AG7" s="87"/>
+      <c r="AH7" s="87"/>
+      <c r="AI7" s="87"/>
+      <c r="AJ7" s="87"/>
+      <c r="AK7" s="87"/>
+      <c r="AL7" s="87"/>
+      <c r="AM7" s="60"/>
     </row>
     <row r="8" spans="1:40">
-      <c r="A8" s="60"/>
+      <c r="A8" s="59"/>
       <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
@@ -1822,54 +1911,54 @@
         <v>2</v>
       </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="152"/>
+      <c r="H8" s="152"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="11"/>
+      <c r="K8" s="152"/>
+      <c r="L8" s="154"/>
+      <c r="M8" s="152"/>
       <c r="N8" s="14"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
+      <c r="O8" s="152"/>
+      <c r="P8" s="152"/>
+      <c r="Q8" s="152"/>
+      <c r="R8" s="152"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="152"/>
       <c r="U8" s="14"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="11"/>
-      <c r="Z8" s="15"/>
-      <c r="AA8" s="15"/>
-      <c r="AB8" s="15"/>
-      <c r="AC8" s="15"/>
-      <c r="AD8" s="15"/>
+      <c r="V8" s="152"/>
+      <c r="W8" s="152"/>
+      <c r="X8" s="152"/>
+      <c r="Y8" s="152"/>
+      <c r="Z8" s="153"/>
+      <c r="AA8" s="153"/>
+      <c r="AB8" s="153"/>
+      <c r="AC8" s="153"/>
+      <c r="AD8" s="153"/>
       <c r="AE8" s="16"/>
-      <c r="AF8" s="15"/>
-      <c r="AG8" s="15"/>
-      <c r="AH8" s="15"/>
-      <c r="AI8" s="15"/>
-      <c r="AJ8" s="15"/>
-      <c r="AK8" s="15"/>
-      <c r="AL8" s="15"/>
-      <c r="AM8" s="61"/>
+      <c r="AF8" s="153"/>
+      <c r="AG8" s="153"/>
+      <c r="AH8" s="153"/>
+      <c r="AI8" s="153"/>
+      <c r="AJ8" s="153"/>
+      <c r="AK8" s="153"/>
+      <c r="AL8" s="153"/>
+      <c r="AM8" s="60"/>
     </row>
     <row r="9" spans="1:40">
-      <c r="A9" s="60"/>
-      <c r="B9" s="17" t="s">
+      <c r="A9" s="59"/>
+      <c r="B9" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="140">
         <v>1</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="91"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="87"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="19"/>
@@ -1902,10 +1991,10 @@
       <c r="AJ9" s="15"/>
       <c r="AK9" s="15"/>
       <c r="AL9" s="15"/>
-      <c r="AM9" s="61"/>
+      <c r="AM9" s="60"/>
     </row>
     <row r="10" spans="1:40">
-      <c r="A10" s="60"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="20" t="s">
         <v>20</v>
       </c>
@@ -1916,54 +2005,54 @@
         <v>1</v>
       </c>
       <c r="E10" s="18"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="11"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="152"/>
+      <c r="H10" s="152"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="152"/>
+      <c r="K10" s="152"/>
+      <c r="L10" s="154"/>
+      <c r="M10" s="152"/>
       <c r="N10" s="14"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
+      <c r="O10" s="152"/>
+      <c r="P10" s="152"/>
+      <c r="Q10" s="152"/>
+      <c r="R10" s="152"/>
+      <c r="S10" s="152"/>
+      <c r="T10" s="152"/>
       <c r="U10" s="14"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="11"/>
-      <c r="Z10" s="15"/>
-      <c r="AA10" s="15"/>
-      <c r="AB10" s="15"/>
-      <c r="AC10" s="15"/>
-      <c r="AD10" s="15"/>
+      <c r="V10" s="152"/>
+      <c r="W10" s="152"/>
+      <c r="X10" s="152"/>
+      <c r="Y10" s="152"/>
+      <c r="Z10" s="153"/>
+      <c r="AA10" s="153"/>
+      <c r="AB10" s="153"/>
+      <c r="AC10" s="153"/>
+      <c r="AD10" s="153"/>
       <c r="AE10" s="16"/>
-      <c r="AF10" s="15"/>
-      <c r="AG10" s="15"/>
-      <c r="AH10" s="15"/>
-      <c r="AI10" s="15"/>
-      <c r="AJ10" s="15"/>
-      <c r="AK10" s="15"/>
-      <c r="AL10" s="15"/>
-      <c r="AM10" s="61"/>
+      <c r="AF10" s="153"/>
+      <c r="AG10" s="153"/>
+      <c r="AH10" s="153"/>
+      <c r="AI10" s="153"/>
+      <c r="AJ10" s="153"/>
+      <c r="AK10" s="153"/>
+      <c r="AL10" s="153"/>
+      <c r="AM10" s="60"/>
     </row>
     <row r="11" spans="1:40">
-      <c r="A11" s="60"/>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="59"/>
+      <c r="B11" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="140" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="140">
         <v>1</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="91"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="87"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
@@ -1996,158 +2085,162 @@
       <c r="AJ11" s="15"/>
       <c r="AK11" s="15"/>
       <c r="AL11" s="15"/>
-      <c r="AM11" s="61"/>
+      <c r="AM11" s="60"/>
     </row>
     <row r="12" spans="1:40">
-      <c r="A12" s="60"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="17" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="18">
+        <v>2</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="152"/>
+      <c r="H12" s="152"/>
+      <c r="I12" s="152"/>
+      <c r="J12" s="152"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="110"/>
+      <c r="M12" s="152"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="152"/>
+      <c r="P12" s="152"/>
+      <c r="Q12" s="152"/>
+      <c r="R12" s="152"/>
+      <c r="S12" s="152"/>
+      <c r="T12" s="152"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="152"/>
+      <c r="W12" s="152"/>
+      <c r="X12" s="152"/>
+      <c r="Y12" s="152"/>
+      <c r="Z12" s="153"/>
+      <c r="AA12" s="153"/>
+      <c r="AB12" s="153"/>
+      <c r="AC12" s="153"/>
+      <c r="AD12" s="153"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="153"/>
+      <c r="AG12" s="153"/>
+      <c r="AH12" s="153"/>
+      <c r="AI12" s="153"/>
+      <c r="AJ12" s="153"/>
+      <c r="AK12" s="153"/>
+      <c r="AL12" s="153"/>
+      <c r="AM12" s="60"/>
+    </row>
+    <row r="13" spans="1:40">
+      <c r="A13" s="59"/>
+      <c r="B13" s="139" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D13" s="140">
         <v>4</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="14"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="15"/>
-      <c r="AA12" s="15"/>
-      <c r="AB12" s="15"/>
-      <c r="AC12" s="15"/>
-      <c r="AD12" s="15"/>
-      <c r="AE12" s="16"/>
-      <c r="AF12" s="9"/>
-      <c r="AG12" s="15"/>
-      <c r="AH12" s="15"/>
-      <c r="AI12" s="15"/>
-      <c r="AJ12" s="15"/>
-      <c r="AK12" s="15"/>
-      <c r="AL12" s="15"/>
-      <c r="AM12" s="61"/>
-    </row>
-    <row r="13" spans="1:40">
-      <c r="A13" s="60"/>
-      <c r="B13" s="87" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="88" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="88"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="91"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="87"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
+      <c r="J13" s="12"/>
       <c r="K13" s="11"/>
       <c r="L13" s="13"/>
       <c r="M13" s="11"/>
       <c r="N13" s="14"/>
-      <c r="O13" s="11"/>
+      <c r="O13" s="12"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
       <c r="U13" s="14"/>
-      <c r="V13" s="11"/>
+      <c r="V13" s="12"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="15"/>
+      <c r="AB13" s="15"/>
       <c r="AC13" s="15"/>
       <c r="AD13" s="15"/>
       <c r="AE13" s="16"/>
-      <c r="AF13" s="15"/>
+      <c r="AF13" s="9"/>
       <c r="AG13" s="15"/>
       <c r="AH13" s="15"/>
       <c r="AI13" s="15"/>
       <c r="AJ13" s="15"/>
       <c r="AK13" s="15"/>
       <c r="AL13" s="15"/>
-      <c r="AM13" s="61"/>
+      <c r="AM13" s="60"/>
     </row>
     <row r="14" spans="1:40">
-      <c r="A14" s="60"/>
+      <c r="A14" s="59"/>
       <c r="B14" s="17" t="s">
         <v>26</v>
       </c>
       <c r="C14" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="18">
+        <v>1</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="152"/>
+      <c r="H14" s="152"/>
+      <c r="I14" s="152"/>
+      <c r="J14" s="152"/>
+      <c r="K14" s="152"/>
+      <c r="L14" s="154"/>
+      <c r="M14" s="152"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="152"/>
+      <c r="P14" s="152"/>
+      <c r="Q14" s="152"/>
+      <c r="R14" s="153"/>
+      <c r="S14" s="153"/>
+      <c r="T14" s="153"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="128"/>
+      <c r="W14" s="152"/>
+      <c r="X14" s="152"/>
+      <c r="Y14" s="152"/>
+      <c r="Z14" s="153"/>
+      <c r="AA14" s="153"/>
+      <c r="AB14" s="155"/>
+      <c r="AC14" s="155"/>
+      <c r="AD14" s="155"/>
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="153"/>
+      <c r="AG14" s="153"/>
+      <c r="AH14" s="153"/>
+      <c r="AI14" s="153"/>
+      <c r="AJ14" s="153"/>
+      <c r="AK14" s="153"/>
+      <c r="AL14" s="153"/>
+      <c r="AM14" s="60"/>
+    </row>
+    <row r="15" spans="1:40">
+      <c r="A15" s="59"/>
+      <c r="B15" s="141" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="117"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="15"/>
-      <c r="AA14" s="15"/>
-      <c r="AB14" s="15"/>
-      <c r="AC14" s="15"/>
-      <c r="AD14" s="15"/>
-      <c r="AE14" s="16"/>
-      <c r="AF14" s="15"/>
-      <c r="AG14" s="15"/>
-      <c r="AH14" s="15"/>
-      <c r="AI14" s="15"/>
-      <c r="AJ14" s="15"/>
-      <c r="AK14" s="15"/>
-      <c r="AL14" s="15"/>
-      <c r="AM14" s="61"/>
-    </row>
-    <row r="15" spans="1:40">
-      <c r="A15" s="60"/>
-      <c r="B15" s="17" t="s">
+      <c r="C15" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="18">
-        <v>1</v>
-      </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="91"/>
+      <c r="D15" s="142">
+        <v>3</v>
+      </c>
+      <c r="E15" s="142"/>
+      <c r="F15" s="87"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
@@ -2159,19 +2252,19 @@
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
       <c r="U15" s="14"/>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
-      <c r="Z15" s="15"/>
-      <c r="AA15" s="15"/>
-      <c r="AB15" s="109"/>
-      <c r="AC15" s="109"/>
-      <c r="AD15" s="109"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="15"/>
+      <c r="AD15" s="15"/>
       <c r="AE15" s="16"/>
       <c r="AF15" s="15"/>
       <c r="AG15" s="15"/>
@@ -2180,161 +2273,165 @@
       <c r="AJ15" s="15"/>
       <c r="AK15" s="15"/>
       <c r="AL15" s="15"/>
-      <c r="AM15" s="61"/>
+      <c r="AM15" s="60"/>
     </row>
     <row r="16" spans="1:40">
-      <c r="A16" s="60"/>
-      <c r="B16" s="87" t="s">
+      <c r="A16" s="59"/>
+      <c r="B16" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="91"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="11"/>
+      <c r="D16" s="85">
+        <v>1</v>
+      </c>
+      <c r="E16" s="85"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="152"/>
+      <c r="H16" s="152"/>
+      <c r="I16" s="152"/>
+      <c r="J16" s="152"/>
+      <c r="K16" s="152"/>
+      <c r="L16" s="154"/>
+      <c r="M16" s="152"/>
       <c r="N16" s="14"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
+      <c r="O16" s="152"/>
+      <c r="P16" s="152"/>
+      <c r="Q16" s="152"/>
+      <c r="R16" s="152"/>
+      <c r="S16" s="152"/>
+      <c r="T16" s="152"/>
       <c r="U16" s="14"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="11"/>
-      <c r="Z16" s="15"/>
-      <c r="AA16" s="15"/>
-      <c r="AB16" s="15"/>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
+      <c r="V16" s="152"/>
+      <c r="W16" s="152"/>
+      <c r="X16" s="152"/>
+      <c r="Y16" s="152"/>
+      <c r="Z16" s="153"/>
+      <c r="AA16" s="153"/>
+      <c r="AB16" s="153"/>
+      <c r="AC16" s="153"/>
+      <c r="AD16" s="153"/>
       <c r="AE16" s="16"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="15"/>
-      <c r="AH16" s="15"/>
-      <c r="AI16" s="15"/>
-      <c r="AJ16" s="15"/>
+      <c r="AF16" s="153"/>
+      <c r="AG16" s="153"/>
+      <c r="AH16" s="153"/>
+      <c r="AI16" s="153"/>
+      <c r="AJ16" s="153"/>
       <c r="AK16" s="22"/>
-      <c r="AL16" s="15"/>
-      <c r="AM16" s="61"/>
+      <c r="AL16" s="153"/>
+      <c r="AM16" s="60"/>
     </row>
     <row r="17" spans="1:39">
-      <c r="A17" s="60"/>
-      <c r="B17" s="90" t="s">
+      <c r="A17" s="59"/>
+      <c r="B17" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="90"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="92"/>
-      <c r="M17" s="91"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="87"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="88"/>
+      <c r="M17" s="87"/>
       <c r="N17" s="23"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="91"/>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="91"/>
-      <c r="T17" s="91"/>
+      <c r="O17" s="87"/>
+      <c r="P17" s="87"/>
+      <c r="Q17" s="87"/>
+      <c r="R17" s="87"/>
+      <c r="S17" s="87"/>
+      <c r="T17" s="87"/>
       <c r="U17" s="23"/>
-      <c r="V17" s="91"/>
-      <c r="W17" s="91"/>
-      <c r="X17" s="91"/>
-      <c r="Y17" s="91"/>
-      <c r="Z17" s="91"/>
-      <c r="AA17" s="91"/>
-      <c r="AB17" s="91"/>
-      <c r="AC17" s="91"/>
-      <c r="AD17" s="91"/>
+      <c r="V17" s="87"/>
+      <c r="W17" s="87"/>
+      <c r="X17" s="87"/>
+      <c r="Y17" s="87"/>
+      <c r="Z17" s="87"/>
+      <c r="AA17" s="87"/>
+      <c r="AB17" s="87"/>
+      <c r="AC17" s="87"/>
+      <c r="AD17" s="87"/>
       <c r="AE17" s="23"/>
-      <c r="AF17" s="91"/>
-      <c r="AG17" s="91"/>
-      <c r="AH17" s="91"/>
-      <c r="AI17" s="91"/>
-      <c r="AJ17" s="91"/>
-      <c r="AK17" s="91"/>
-      <c r="AL17" s="91"/>
-      <c r="AM17" s="61"/>
+      <c r="AF17" s="87"/>
+      <c r="AG17" s="87"/>
+      <c r="AH17" s="87"/>
+      <c r="AI17" s="87"/>
+      <c r="AJ17" s="87"/>
+      <c r="AK17" s="87"/>
+      <c r="AL17" s="87"/>
+      <c r="AM17" s="60"/>
     </row>
     <row r="18" spans="1:39">
-      <c r="A18" s="60"/>
+      <c r="A18" s="59"/>
       <c r="B18" s="24" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="25"/>
+      <c r="D18" s="25">
+        <v>2</v>
+      </c>
       <c r="E18" s="25"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="116"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="152"/>
+      <c r="H18" s="152"/>
+      <c r="I18" s="152"/>
+      <c r="J18" s="152"/>
+      <c r="K18" s="152"/>
+      <c r="L18" s="108"/>
+      <c r="M18" s="109"/>
       <c r="N18" s="14"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
+      <c r="O18" s="152"/>
+      <c r="P18" s="152"/>
+      <c r="Q18" s="152"/>
+      <c r="R18" s="152"/>
+      <c r="S18" s="152"/>
+      <c r="T18" s="152"/>
       <c r="U18" s="14"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="11"/>
-      <c r="Z18" s="15"/>
-      <c r="AA18" s="15"/>
-      <c r="AB18" s="15"/>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
+      <c r="V18" s="152"/>
+      <c r="W18" s="152"/>
+      <c r="X18" s="152"/>
+      <c r="Y18" s="152"/>
+      <c r="Z18" s="153"/>
+      <c r="AA18" s="153"/>
+      <c r="AB18" s="153"/>
+      <c r="AC18" s="153"/>
+      <c r="AD18" s="153"/>
       <c r="AE18" s="16"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
-      <c r="AI18" s="15"/>
-      <c r="AJ18" s="15"/>
-      <c r="AK18" s="15"/>
-      <c r="AL18" s="15"/>
-      <c r="AM18" s="61"/>
+      <c r="AF18" s="153"/>
+      <c r="AG18" s="153"/>
+      <c r="AH18" s="153"/>
+      <c r="AI18" s="153"/>
+      <c r="AJ18" s="153"/>
+      <c r="AK18" s="153"/>
+      <c r="AL18" s="153"/>
+      <c r="AM18" s="60"/>
     </row>
     <row r="19" spans="1:39">
-      <c r="A19" s="60"/>
-      <c r="B19" s="24" t="s">
+      <c r="A19" s="59"/>
+      <c r="B19" s="131" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="132">
         <v>1</v>
       </c>
-      <c r="E19" s="25"/>
-      <c r="F19" s="91"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="87"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="13"/>
-      <c r="M19" s="116"/>
+      <c r="M19" s="109"/>
       <c r="N19" s="14"/>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
@@ -2360,11 +2457,11 @@
       <c r="AJ19" s="15"/>
       <c r="AK19" s="15"/>
       <c r="AL19" s="15"/>
-      <c r="AM19" s="61"/>
+      <c r="AM19" s="60"/>
     </row>
     <row r="20" spans="1:39">
-      <c r="A20" s="60"/>
-      <c r="B20" s="89" t="s">
+      <c r="A20" s="59"/>
+      <c r="B20" s="86" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="25" t="s">
@@ -2374,52 +2471,54 @@
         <v>4</v>
       </c>
       <c r="E20" s="25"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="116"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="152"/>
+      <c r="H20" s="152"/>
+      <c r="I20" s="152"/>
+      <c r="J20" s="152"/>
+      <c r="K20" s="152"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
       <c r="N20" s="14"/>
-      <c r="O20" s="115"/>
-      <c r="P20" s="116"/>
-      <c r="Q20" s="108"/>
-      <c r="R20" s="123"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
+      <c r="O20" s="108"/>
+      <c r="P20" s="109"/>
+      <c r="Q20" s="156"/>
+      <c r="R20" s="157"/>
+      <c r="S20" s="152"/>
+      <c r="T20" s="152"/>
       <c r="U20" s="14"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="11"/>
-      <c r="Z20" s="15"/>
-      <c r="AA20" s="15"/>
-      <c r="AB20" s="15"/>
-      <c r="AC20" s="15"/>
-      <c r="AD20" s="15"/>
+      <c r="V20" s="152"/>
+      <c r="W20" s="152"/>
+      <c r="X20" s="152"/>
+      <c r="Y20" s="152"/>
+      <c r="Z20" s="153"/>
+      <c r="AA20" s="153"/>
+      <c r="AB20" s="153"/>
+      <c r="AC20" s="153"/>
+      <c r="AD20" s="153"/>
       <c r="AE20" s="16"/>
-      <c r="AF20" s="15"/>
-      <c r="AG20" s="15"/>
-      <c r="AH20" s="15"/>
-      <c r="AI20" s="15"/>
-      <c r="AJ20" s="15"/>
-      <c r="AK20" s="15"/>
-      <c r="AL20" s="15"/>
-      <c r="AM20" s="61"/>
+      <c r="AF20" s="153"/>
+      <c r="AG20" s="153"/>
+      <c r="AH20" s="153"/>
+      <c r="AI20" s="153"/>
+      <c r="AJ20" s="153"/>
+      <c r="AK20" s="153"/>
+      <c r="AL20" s="153"/>
+      <c r="AM20" s="60"/>
     </row>
     <row r="21" spans="1:39">
-      <c r="A21" s="60"/>
-      <c r="B21" s="24" t="s">
+      <c r="A21" s="59"/>
+      <c r="B21" s="131" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="91"/>
+      <c r="D21" s="132">
+        <v>3</v>
+      </c>
+      <c r="E21" s="132"/>
+      <c r="F21" s="87"/>
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
@@ -2430,18 +2529,18 @@
       <c r="N21" s="14"/>
       <c r="O21" s="11"/>
       <c r="P21" s="11"/>
-      <c r="Q21" s="116"/>
-      <c r="R21" s="116"/>
-      <c r="S21" s="116"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
       <c r="T21" s="11"/>
       <c r="U21" s="14"/>
       <c r="V21" s="11"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
-      <c r="Z21" s="125"/>
-      <c r="AA21" s="109"/>
-      <c r="AB21" s="126"/>
+      <c r="Z21" s="116"/>
+      <c r="AA21" s="103"/>
+      <c r="AB21" s="117"/>
       <c r="AC21" s="15"/>
       <c r="AD21" s="15"/>
       <c r="AE21" s="16"/>
@@ -2452,64 +2551,68 @@
       <c r="AJ21" s="15"/>
       <c r="AK21" s="15"/>
       <c r="AL21" s="15"/>
-      <c r="AM21" s="61"/>
+      <c r="AM21" s="60"/>
     </row>
     <row r="22" spans="1:39">
-      <c r="A22" s="60"/>
+      <c r="A22" s="59"/>
       <c r="B22" s="24" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="25"/>
+      <c r="D22" s="25">
+        <v>1</v>
+      </c>
       <c r="E22" s="25"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="11"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="152"/>
+      <c r="H22" s="152"/>
+      <c r="I22" s="152"/>
+      <c r="J22" s="152"/>
+      <c r="K22" s="152"/>
+      <c r="L22" s="154"/>
+      <c r="M22" s="152"/>
       <c r="N22" s="14"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="116"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
+      <c r="O22" s="152"/>
+      <c r="P22" s="152"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="152"/>
+      <c r="S22" s="152"/>
+      <c r="T22" s="152"/>
       <c r="U22" s="14"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-      <c r="Z22" s="127"/>
-      <c r="AA22" s="15"/>
-      <c r="AB22" s="128"/>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="15"/>
+      <c r="V22" s="152"/>
+      <c r="W22" s="152"/>
+      <c r="X22" s="152"/>
+      <c r="Y22" s="152"/>
+      <c r="Z22" s="158"/>
+      <c r="AA22" s="153"/>
+      <c r="AB22" s="159"/>
+      <c r="AC22" s="153"/>
+      <c r="AD22" s="153"/>
       <c r="AE22" s="16"/>
-      <c r="AF22" s="15"/>
-      <c r="AG22" s="15"/>
-      <c r="AH22" s="15"/>
-      <c r="AI22" s="15"/>
-      <c r="AJ22" s="15"/>
-      <c r="AK22" s="15"/>
-      <c r="AL22" s="15"/>
-      <c r="AM22" s="61"/>
+      <c r="AF22" s="153"/>
+      <c r="AG22" s="153"/>
+      <c r="AH22" s="153"/>
+      <c r="AI22" s="153"/>
+      <c r="AJ22" s="153"/>
+      <c r="AK22" s="153"/>
+      <c r="AL22" s="153"/>
+      <c r="AM22" s="60"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="60"/>
-      <c r="B23" s="93" t="s">
+      <c r="A23" s="59"/>
+      <c r="B23" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="91"/>
+      <c r="D23" s="132">
+        <v>2</v>
+      </c>
+      <c r="E23" s="132"/>
+      <c r="F23" s="87"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -2520,8 +2623,8 @@
       <c r="N23" s="14"/>
       <c r="O23" s="11"/>
       <c r="P23" s="11"/>
-      <c r="Q23" s="116"/>
-      <c r="R23" s="116"/>
+      <c r="Q23" s="109"/>
+      <c r="R23" s="109"/>
       <c r="S23" s="11"/>
       <c r="T23" s="11"/>
       <c r="U23" s="14"/>
@@ -2529,9 +2632,9 @@
       <c r="W23" s="11"/>
       <c r="X23" s="11"/>
       <c r="Y23" s="11"/>
-      <c r="Z23" s="127"/>
+      <c r="Z23" s="118"/>
       <c r="AA23" s="15"/>
-      <c r="AB23" s="128"/>
+      <c r="AB23" s="119"/>
       <c r="AC23" s="15"/>
       <c r="AD23" s="15"/>
       <c r="AE23" s="16"/>
@@ -2542,64 +2645,68 @@
       <c r="AJ23" s="15"/>
       <c r="AK23" s="15"/>
       <c r="AL23" s="15"/>
-      <c r="AM23" s="61"/>
+      <c r="AM23" s="60"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="60"/>
+      <c r="A24" s="59"/>
       <c r="B24" s="24" t="s">
         <v>40</v>
       </c>
       <c r="C24" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="25"/>
+      <c r="D24" s="25">
+        <v>3</v>
+      </c>
       <c r="E24" s="25"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="11"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="152"/>
+      <c r="H24" s="152"/>
+      <c r="I24" s="152"/>
+      <c r="J24" s="152"/>
+      <c r="K24" s="152"/>
+      <c r="L24" s="154"/>
+      <c r="M24" s="152"/>
       <c r="N24" s="14"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="116"/>
-      <c r="S24" s="116"/>
-      <c r="T24" s="116"/>
+      <c r="O24" s="152"/>
+      <c r="P24" s="152"/>
+      <c r="Q24" s="152"/>
+      <c r="R24" s="109"/>
+      <c r="S24" s="109"/>
+      <c r="T24" s="109"/>
       <c r="U24" s="14"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="11"/>
-      <c r="Z24" s="127"/>
-      <c r="AA24" s="15"/>
-      <c r="AB24" s="128"/>
-      <c r="AC24" s="15"/>
-      <c r="AD24" s="15"/>
+      <c r="V24" s="152"/>
+      <c r="W24" s="152"/>
+      <c r="X24" s="152"/>
+      <c r="Y24" s="152"/>
+      <c r="Z24" s="158"/>
+      <c r="AA24" s="153"/>
+      <c r="AB24" s="159"/>
+      <c r="AC24" s="153"/>
+      <c r="AD24" s="153"/>
       <c r="AE24" s="16"/>
-      <c r="AF24" s="15"/>
-      <c r="AG24" s="15"/>
-      <c r="AH24" s="15"/>
-      <c r="AI24" s="15"/>
-      <c r="AJ24" s="15"/>
-      <c r="AK24" s="15"/>
-      <c r="AL24" s="15"/>
-      <c r="AM24" s="61"/>
+      <c r="AF24" s="153"/>
+      <c r="AG24" s="153"/>
+      <c r="AH24" s="153"/>
+      <c r="AI24" s="153"/>
+      <c r="AJ24" s="153"/>
+      <c r="AK24" s="153"/>
+      <c r="AL24" s="153"/>
+      <c r="AM24" s="60"/>
     </row>
     <row r="25" spans="1:39">
-      <c r="A25" s="60"/>
-      <c r="B25" s="24" t="s">
+      <c r="A25" s="59"/>
+      <c r="B25" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="91"/>
+      <c r="D25" s="132">
+        <v>3</v>
+      </c>
+      <c r="E25" s="132"/>
+      <c r="F25" s="87"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
@@ -2615,9 +2722,9 @@
       <c r="S25" s="11"/>
       <c r="T25" s="11"/>
       <c r="U25" s="14"/>
-      <c r="V25" s="107"/>
-      <c r="W25" s="107"/>
-      <c r="X25" s="107"/>
+      <c r="V25" s="102"/>
+      <c r="W25" s="102"/>
+      <c r="X25" s="102"/>
       <c r="Y25" s="11"/>
       <c r="Z25" s="15"/>
       <c r="AA25" s="15"/>
@@ -2632,60 +2739,68 @@
       <c r="AJ25" s="15"/>
       <c r="AK25" s="15"/>
       <c r="AL25" s="15"/>
-      <c r="AM25" s="61"/>
+      <c r="AM25" s="60"/>
     </row>
     <row r="26" spans="1:39">
-      <c r="A26" s="60"/>
+      <c r="A26" s="59"/>
       <c r="B26" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
+      <c r="C26" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="25">
+        <v>3</v>
+      </c>
       <c r="E26" s="25"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="11"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="152"/>
+      <c r="H26" s="152"/>
+      <c r="I26" s="152"/>
+      <c r="J26" s="152"/>
+      <c r="K26" s="152"/>
+      <c r="L26" s="154"/>
+      <c r="M26" s="152"/>
       <c r="N26" s="14"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
+      <c r="O26" s="152"/>
+      <c r="P26" s="152"/>
+      <c r="Q26" s="152"/>
+      <c r="R26" s="152"/>
+      <c r="S26" s="152"/>
+      <c r="T26" s="152"/>
       <c r="U26" s="14"/>
-      <c r="V26" s="11"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="11"/>
-      <c r="Z26" s="124"/>
-      <c r="AA26" s="124"/>
-      <c r="AB26" s="124"/>
-      <c r="AC26" s="13"/>
-      <c r="AD26" s="13"/>
+      <c r="V26" s="152"/>
+      <c r="W26" s="152"/>
+      <c r="X26" s="152"/>
+      <c r="Y26" s="152"/>
+      <c r="Z26" s="115"/>
+      <c r="AA26" s="115"/>
+      <c r="AB26" s="115"/>
+      <c r="AC26" s="154"/>
+      <c r="AD26" s="154"/>
       <c r="AE26" s="16"/>
-      <c r="AF26" s="15"/>
-      <c r="AG26" s="15"/>
-      <c r="AH26" s="15"/>
-      <c r="AI26" s="15"/>
-      <c r="AJ26" s="15"/>
-      <c r="AK26" s="15"/>
-      <c r="AL26" s="15"/>
-      <c r="AM26" s="61"/>
+      <c r="AF26" s="153"/>
+      <c r="AG26" s="153"/>
+      <c r="AH26" s="153"/>
+      <c r="AI26" s="153"/>
+      <c r="AJ26" s="153"/>
+      <c r="AK26" s="153"/>
+      <c r="AL26" s="153"/>
+      <c r="AM26" s="60"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="60"/>
-      <c r="B27" s="24" t="s">
+      <c r="A27" s="59"/>
+      <c r="B27" s="131" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="91"/>
+      <c r="C27" s="132" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="132">
+        <v>3</v>
+      </c>
+      <c r="E27" s="132"/>
+      <c r="F27" s="87"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
@@ -2705,9 +2820,9 @@
       <c r="W27" s="11"/>
       <c r="X27" s="11"/>
       <c r="Y27" s="11"/>
-      <c r="Z27" s="124"/>
-      <c r="AA27" s="124"/>
-      <c r="AB27" s="124"/>
+      <c r="Z27" s="115"/>
+      <c r="AA27" s="115"/>
+      <c r="AB27" s="115"/>
       <c r="AC27" s="13"/>
       <c r="AD27" s="13"/>
       <c r="AE27" s="16"/>
@@ -2718,60 +2833,68 @@
       <c r="AJ27" s="15"/>
       <c r="AK27" s="15"/>
       <c r="AL27" s="15"/>
-      <c r="AM27" s="61"/>
+      <c r="AM27" s="60"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="60"/>
+      <c r="A28" s="59"/>
       <c r="B28" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
+      <c r="C28" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="25">
+        <v>3</v>
+      </c>
       <c r="E28" s="25"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="11"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="152"/>
+      <c r="H28" s="152"/>
+      <c r="I28" s="152"/>
+      <c r="J28" s="152"/>
+      <c r="K28" s="152"/>
+      <c r="L28" s="154"/>
+      <c r="M28" s="152"/>
       <c r="N28" s="14"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="11"/>
-      <c r="S28" s="11"/>
-      <c r="T28" s="11"/>
+      <c r="O28" s="152"/>
+      <c r="P28" s="152"/>
+      <c r="Q28" s="152"/>
+      <c r="R28" s="152"/>
+      <c r="S28" s="152"/>
+      <c r="T28" s="152"/>
       <c r="U28" s="14"/>
-      <c r="V28" s="11"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="11"/>
-      <c r="Z28" s="124"/>
-      <c r="AA28" s="124"/>
-      <c r="AB28" s="124"/>
-      <c r="AC28" s="13"/>
-      <c r="AD28" s="13"/>
+      <c r="V28" s="152"/>
+      <c r="W28" s="152"/>
+      <c r="X28" s="152"/>
+      <c r="Y28" s="152"/>
+      <c r="Z28" s="115"/>
+      <c r="AA28" s="115"/>
+      <c r="AB28" s="115"/>
+      <c r="AC28" s="154"/>
+      <c r="AD28" s="154"/>
       <c r="AE28" s="16"/>
-      <c r="AF28" s="15"/>
-      <c r="AG28" s="15"/>
-      <c r="AH28" s="15"/>
-      <c r="AI28" s="15"/>
-      <c r="AJ28" s="15"/>
-      <c r="AK28" s="15"/>
-      <c r="AL28" s="15"/>
-      <c r="AM28" s="61"/>
+      <c r="AF28" s="153"/>
+      <c r="AG28" s="153"/>
+      <c r="AH28" s="153"/>
+      <c r="AI28" s="153"/>
+      <c r="AJ28" s="153"/>
+      <c r="AK28" s="153"/>
+      <c r="AL28" s="153"/>
+      <c r="AM28" s="60"/>
     </row>
     <row r="29" spans="1:39">
-      <c r="A29" s="60"/>
-      <c r="B29" s="24" t="s">
+      <c r="A29" s="59"/>
+      <c r="B29" s="131" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="91"/>
+      <c r="C29" s="132" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="132">
+        <v>3</v>
+      </c>
+      <c r="E29" s="132"/>
+      <c r="F29" s="87"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -2791,9 +2914,9 @@
       <c r="W29" s="11"/>
       <c r="X29" s="11"/>
       <c r="Y29" s="11"/>
-      <c r="Z29" s="124"/>
-      <c r="AA29" s="124"/>
-      <c r="AB29" s="124"/>
+      <c r="Z29" s="115"/>
+      <c r="AA29" s="115"/>
+      <c r="AB29" s="115"/>
       <c r="AC29" s="13"/>
       <c r="AD29" s="13"/>
       <c r="AE29" s="16"/>
@@ -2804,66 +2927,68 @@
       <c r="AJ29" s="15"/>
       <c r="AK29" s="15"/>
       <c r="AL29" s="15"/>
-      <c r="AM29" s="61"/>
+      <c r="AM29" s="60"/>
     </row>
     <row r="30" spans="1:39">
-      <c r="A30" s="60"/>
+      <c r="A30" s="59"/>
       <c r="B30" s="24" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="25"/>
+      <c r="D30" s="25">
+        <v>2</v>
+      </c>
       <c r="E30" s="25"/>
-      <c r="F30" s="91"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="11"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="152"/>
+      <c r="H30" s="152"/>
+      <c r="I30" s="152"/>
+      <c r="J30" s="152"/>
+      <c r="K30" s="152"/>
+      <c r="L30" s="154"/>
+      <c r="M30" s="152"/>
       <c r="N30" s="14"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="11"/>
-      <c r="T30" s="11"/>
+      <c r="O30" s="152"/>
+      <c r="P30" s="152"/>
+      <c r="Q30" s="152"/>
+      <c r="R30" s="152"/>
+      <c r="S30" s="152"/>
+      <c r="T30" s="152"/>
       <c r="U30" s="14"/>
-      <c r="V30" s="11"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="11"/>
-      <c r="Z30" s="15"/>
-      <c r="AA30" s="15"/>
-      <c r="AB30" s="15"/>
-      <c r="AC30" s="114"/>
-      <c r="AD30" s="114"/>
+      <c r="V30" s="152"/>
+      <c r="W30" s="152"/>
+      <c r="X30" s="152"/>
+      <c r="Y30" s="152"/>
+      <c r="Z30" s="153"/>
+      <c r="AA30" s="153"/>
+      <c r="AB30" s="153"/>
+      <c r="AC30" s="107"/>
+      <c r="AD30" s="107"/>
       <c r="AE30" s="16"/>
-      <c r="AF30" s="15"/>
-      <c r="AG30" s="15"/>
-      <c r="AH30" s="15"/>
-      <c r="AI30" s="15"/>
-      <c r="AJ30" s="15"/>
-      <c r="AK30" s="15"/>
-      <c r="AL30" s="15"/>
-      <c r="AM30" s="61"/>
+      <c r="AF30" s="153"/>
+      <c r="AG30" s="153"/>
+      <c r="AH30" s="153"/>
+      <c r="AI30" s="153"/>
+      <c r="AJ30" s="153"/>
+      <c r="AK30" s="153"/>
+      <c r="AL30" s="153"/>
+      <c r="AM30" s="60"/>
     </row>
     <row r="31" spans="1:39">
-      <c r="A31" s="60"/>
-      <c r="B31" s="24" t="s">
+      <c r="A31" s="59"/>
+      <c r="B31" s="131" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="132">
         <v>2</v>
       </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="91"/>
+      <c r="E31" s="132"/>
+      <c r="F31" s="87"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2886,8 +3011,8 @@
       <c r="Z31" s="15"/>
       <c r="AA31" s="15"/>
       <c r="AB31" s="15"/>
-      <c r="AC31" s="114"/>
-      <c r="AD31" s="114"/>
+      <c r="AC31" s="107"/>
+      <c r="AD31" s="107"/>
       <c r="AE31" s="16"/>
       <c r="AF31" s="15"/>
       <c r="AG31" s="15"/>
@@ -2896,53 +3021,53 @@
       <c r="AJ31" s="15"/>
       <c r="AK31" s="15"/>
       <c r="AL31" s="15"/>
-      <c r="AM31" s="61"/>
+      <c r="AM31" s="60"/>
     </row>
     <row r="32" spans="1:39">
-      <c r="A32" s="60"/>
+      <c r="A32" s="59"/>
       <c r="B32" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
-      <c r="F32" s="91"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="91"/>
-      <c r="K32" s="91"/>
-      <c r="L32" s="92"/>
-      <c r="M32" s="91"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="87"/>
+      <c r="I32" s="87"/>
+      <c r="J32" s="87"/>
+      <c r="K32" s="87"/>
+      <c r="L32" s="88"/>
+      <c r="M32" s="87"/>
       <c r="N32" s="23"/>
-      <c r="O32" s="91"/>
-      <c r="P32" s="91"/>
-      <c r="Q32" s="91"/>
-      <c r="R32" s="91"/>
-      <c r="S32" s="91"/>
-      <c r="T32" s="91"/>
+      <c r="O32" s="87"/>
+      <c r="P32" s="87"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="87"/>
+      <c r="S32" s="87"/>
+      <c r="T32" s="87"/>
       <c r="U32" s="23"/>
-      <c r="V32" s="91"/>
-      <c r="W32" s="91"/>
-      <c r="X32" s="91"/>
-      <c r="Y32" s="91"/>
-      <c r="Z32" s="91"/>
-      <c r="AA32" s="91"/>
-      <c r="AB32" s="91"/>
-      <c r="AC32" s="91"/>
-      <c r="AD32" s="91"/>
+      <c r="V32" s="87"/>
+      <c r="W32" s="87"/>
+      <c r="X32" s="87"/>
+      <c r="Y32" s="87"/>
+      <c r="Z32" s="87"/>
+      <c r="AA32" s="87"/>
+      <c r="AB32" s="87"/>
+      <c r="AC32" s="87"/>
+      <c r="AD32" s="87"/>
       <c r="AE32" s="23"/>
-      <c r="AF32" s="91"/>
-      <c r="AG32" s="91"/>
-      <c r="AH32" s="91"/>
-      <c r="AI32" s="91"/>
-      <c r="AJ32" s="91"/>
-      <c r="AK32" s="91"/>
-      <c r="AL32" s="91"/>
-      <c r="AM32" s="61"/>
+      <c r="AF32" s="87"/>
+      <c r="AG32" s="87"/>
+      <c r="AH32" s="87"/>
+      <c r="AI32" s="87"/>
+      <c r="AJ32" s="87"/>
+      <c r="AK32" s="87"/>
+      <c r="AL32" s="87"/>
+      <c r="AM32" s="60"/>
     </row>
     <row r="33" spans="1:41">
-      <c r="A33" s="60"/>
+      <c r="A33" s="59"/>
       <c r="B33" s="27" t="s">
         <v>50</v>
       </c>
@@ -2953,54 +3078,54 @@
         <v>1</v>
       </c>
       <c r="E33" s="28"/>
-      <c r="F33" s="91"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="152"/>
+      <c r="H33" s="152"/>
+      <c r="I33" s="152"/>
       <c r="J33" s="30"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="11"/>
+      <c r="K33" s="152"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="152"/>
       <c r="N33" s="14"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-      <c r="R33" s="11"/>
-      <c r="S33" s="11"/>
-      <c r="T33" s="11"/>
+      <c r="O33" s="152"/>
+      <c r="P33" s="152"/>
+      <c r="Q33" s="152"/>
+      <c r="R33" s="152"/>
+      <c r="S33" s="152"/>
+      <c r="T33" s="152"/>
       <c r="U33" s="14"/>
-      <c r="V33" s="11"/>
-      <c r="W33" s="11"/>
-      <c r="X33" s="11"/>
-      <c r="Y33" s="11"/>
-      <c r="Z33" s="15"/>
-      <c r="AA33" s="15"/>
-      <c r="AB33" s="15"/>
-      <c r="AC33" s="15"/>
-      <c r="AD33" s="15"/>
+      <c r="V33" s="152"/>
+      <c r="W33" s="152"/>
+      <c r="X33" s="152"/>
+      <c r="Y33" s="152"/>
+      <c r="Z33" s="153"/>
+      <c r="AA33" s="153"/>
+      <c r="AB33" s="153"/>
+      <c r="AC33" s="153"/>
+      <c r="AD33" s="153"/>
       <c r="AE33" s="16"/>
-      <c r="AF33" s="15"/>
-      <c r="AG33" s="15"/>
-      <c r="AH33" s="15"/>
-      <c r="AI33" s="15"/>
-      <c r="AJ33" s="15"/>
-      <c r="AK33" s="15"/>
-      <c r="AL33" s="15"/>
-      <c r="AM33" s="61"/>
+      <c r="AF33" s="153"/>
+      <c r="AG33" s="153"/>
+      <c r="AH33" s="153"/>
+      <c r="AI33" s="153"/>
+      <c r="AJ33" s="153"/>
+      <c r="AK33" s="153"/>
+      <c r="AL33" s="153"/>
+      <c r="AM33" s="60"/>
     </row>
     <row r="34" spans="1:41">
-      <c r="A34" s="60"/>
-      <c r="B34" s="27" t="s">
+      <c r="A34" s="59"/>
+      <c r="B34" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="135">
         <v>1</v>
       </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="91"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="87"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
@@ -3033,10 +3158,10 @@
       <c r="AJ34" s="15"/>
       <c r="AK34" s="15"/>
       <c r="AL34" s="15"/>
-      <c r="AM34" s="61"/>
+      <c r="AM34" s="60"/>
     </row>
     <row r="35" spans="1:41">
-      <c r="A35" s="60"/>
+      <c r="A35" s="59"/>
       <c r="B35" s="27" t="s">
         <v>52</v>
       </c>
@@ -3047,62 +3172,63 @@
         <v>1</v>
       </c>
       <c r="E35" s="28"/>
-      <c r="F35" s="91"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="118"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="152"/>
+      <c r="H35" s="152"/>
+      <c r="I35" s="152"/>
+      <c r="J35" s="152"/>
+      <c r="K35" s="152"/>
+      <c r="L35" s="154"/>
+      <c r="M35" s="111"/>
       <c r="N35" s="14"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
-      <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
+      <c r="O35" s="152"/>
+      <c r="P35" s="152"/>
+      <c r="Q35" s="152"/>
+      <c r="R35" s="160"/>
+      <c r="S35" s="152"/>
+      <c r="T35" s="152"/>
       <c r="U35" s="14"/>
-      <c r="V35" s="11"/>
-      <c r="W35" s="11"/>
-      <c r="X35" s="11"/>
-      <c r="Y35" s="11"/>
-      <c r="Z35" s="15"/>
-      <c r="AA35" s="15"/>
-      <c r="AB35" s="15"/>
-      <c r="AC35" s="15"/>
-      <c r="AD35" s="15"/>
+      <c r="V35" s="152"/>
+      <c r="W35" s="152"/>
+      <c r="X35" s="152"/>
+      <c r="Y35" s="152"/>
+      <c r="Z35" s="153"/>
+      <c r="AA35" s="153"/>
+      <c r="AB35" s="153"/>
+      <c r="AC35" s="153"/>
+      <c r="AD35" s="153"/>
       <c r="AE35" s="16"/>
-      <c r="AF35" s="15"/>
-      <c r="AG35" s="15"/>
-      <c r="AH35" s="15"/>
-      <c r="AI35" s="15"/>
-      <c r="AJ35" s="15"/>
-      <c r="AK35" s="15"/>
-      <c r="AL35" s="15"/>
-      <c r="AM35" s="61"/>
+      <c r="AF35" s="153"/>
+      <c r="AG35" s="153"/>
+      <c r="AH35" s="153"/>
+      <c r="AI35" s="153"/>
+      <c r="AJ35" s="153"/>
+      <c r="AK35" s="153"/>
+      <c r="AL35" s="153"/>
+      <c r="AM35" s="60"/>
     </row>
     <row r="36" spans="1:41">
-      <c r="A36" s="60"/>
-      <c r="B36" s="27" t="s">
+      <c r="A36" s="59"/>
+      <c r="B36" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="135" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="28">
+      <c r="D36" s="135">
         <v>1</v>
       </c>
-      <c r="E36" s="28"/>
-      <c r="F36" s="91"/>
+      <c r="E36" s="135"/>
+      <c r="F36" s="87"/>
       <c r="G36" s="11"/>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
       <c r="L36" s="13"/>
-      <c r="M36" s="118"/>
+      <c r="M36" s="111"/>
       <c r="N36" s="14"/>
-      <c r="O36" s="119"/>
+      <c r="O36" s="112"/>
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
       <c r="R36" s="11"/>
@@ -3126,10 +3252,10 @@
       <c r="AJ36" s="15"/>
       <c r="AK36" s="15"/>
       <c r="AL36" s="15"/>
-      <c r="AM36" s="61"/>
+      <c r="AM36" s="60"/>
     </row>
     <row r="37" spans="1:41">
-      <c r="A37" s="60"/>
+      <c r="A37" s="59"/>
       <c r="B37" s="27" t="s">
         <v>56</v>
       </c>
@@ -3140,63 +3266,63 @@
         <v>1</v>
       </c>
       <c r="E37" s="28"/>
-      <c r="F37" s="91"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="118"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="152"/>
+      <c r="H37" s="152"/>
+      <c r="I37" s="152"/>
+      <c r="J37" s="152"/>
+      <c r="K37" s="152"/>
+      <c r="L37" s="154"/>
+      <c r="M37" s="111"/>
       <c r="N37" s="14"/>
-      <c r="O37" s="120"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="11"/>
-      <c r="S37" s="11"/>
-      <c r="T37" s="11"/>
+      <c r="O37" s="161"/>
+      <c r="P37" s="152"/>
+      <c r="Q37" s="152"/>
+      <c r="R37" s="152"/>
+      <c r="S37" s="152"/>
+      <c r="T37" s="152"/>
       <c r="U37" s="14"/>
-      <c r="V37" s="11"/>
-      <c r="W37" s="11"/>
-      <c r="X37" s="11"/>
-      <c r="Y37" s="11"/>
-      <c r="Z37" s="15"/>
-      <c r="AA37" s="15"/>
-      <c r="AB37" s="15"/>
-      <c r="AC37" s="15"/>
-      <c r="AD37" s="15"/>
+      <c r="V37" s="152"/>
+      <c r="W37" s="152"/>
+      <c r="X37" s="152"/>
+      <c r="Y37" s="152"/>
+      <c r="Z37" s="153"/>
+      <c r="AA37" s="153"/>
+      <c r="AB37" s="153"/>
+      <c r="AC37" s="153"/>
+      <c r="AD37" s="153"/>
       <c r="AE37" s="16"/>
-      <c r="AF37" s="15"/>
-      <c r="AG37" s="15"/>
-      <c r="AH37" s="15"/>
-      <c r="AI37" s="15"/>
-      <c r="AJ37" s="15"/>
-      <c r="AK37" s="15"/>
-      <c r="AL37" s="15"/>
-      <c r="AM37" s="61"/>
+      <c r="AF37" s="153"/>
+      <c r="AG37" s="153"/>
+      <c r="AH37" s="153"/>
+      <c r="AI37" s="153"/>
+      <c r="AJ37" s="153"/>
+      <c r="AK37" s="153"/>
+      <c r="AL37" s="153"/>
+      <c r="AM37" s="60"/>
     </row>
     <row r="38" spans="1:41">
-      <c r="A38" s="60"/>
-      <c r="B38" s="27" t="s">
+      <c r="A38" s="59"/>
+      <c r="B38" s="134" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="135" t="s">
         <v>38</v>
       </c>
-      <c r="D38" s="28">
+      <c r="D38" s="135">
         <v>1</v>
       </c>
-      <c r="E38" s="28"/>
-      <c r="F38" s="91"/>
+      <c r="E38" s="135"/>
+      <c r="F38" s="87"/>
       <c r="G38" s="11"/>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="13"/>
-      <c r="M38" s="118"/>
+      <c r="M38" s="111"/>
       <c r="N38" s="14"/>
-      <c r="O38" s="121"/>
+      <c r="O38" s="113"/>
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
@@ -3220,10 +3346,10 @@
       <c r="AJ38" s="15"/>
       <c r="AK38" s="15"/>
       <c r="AL38" s="15"/>
-      <c r="AM38" s="61"/>
+      <c r="AM38" s="60"/>
     </row>
     <row r="39" spans="1:41">
-      <c r="A39" s="60"/>
+      <c r="A39" s="59"/>
       <c r="B39" s="27" t="s">
         <v>58</v>
       </c>
@@ -3234,54 +3360,54 @@
         <v>1</v>
       </c>
       <c r="E39" s="28"/>
-      <c r="F39" s="91"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="11"/>
+      <c r="F39" s="87"/>
+      <c r="G39" s="152"/>
+      <c r="H39" s="152"/>
+      <c r="I39" s="152"/>
+      <c r="J39" s="152"/>
+      <c r="K39" s="152"/>
+      <c r="L39" s="154"/>
+      <c r="M39" s="152"/>
       <c r="N39" s="14"/>
-      <c r="O39" s="118"/>
-      <c r="P39" s="11"/>
-      <c r="Q39" s="11"/>
-      <c r="R39" s="11"/>
-      <c r="S39" s="11"/>
-      <c r="T39" s="11"/>
+      <c r="O39" s="111"/>
+      <c r="P39" s="152"/>
+      <c r="Q39" s="152"/>
+      <c r="R39" s="152"/>
+      <c r="S39" s="152"/>
+      <c r="T39" s="152"/>
       <c r="U39" s="14"/>
-      <c r="V39" s="11"/>
-      <c r="W39" s="11"/>
-      <c r="X39" s="11"/>
-      <c r="Y39" s="11"/>
-      <c r="Z39" s="15"/>
-      <c r="AA39" s="15"/>
-      <c r="AB39" s="15"/>
-      <c r="AC39" s="15"/>
-      <c r="AD39" s="15"/>
+      <c r="V39" s="152"/>
+      <c r="W39" s="152"/>
+      <c r="X39" s="152"/>
+      <c r="Y39" s="152"/>
+      <c r="Z39" s="153"/>
+      <c r="AA39" s="153"/>
+      <c r="AB39" s="153"/>
+      <c r="AC39" s="153"/>
+      <c r="AD39" s="153"/>
       <c r="AE39" s="16"/>
-      <c r="AF39" s="15"/>
-      <c r="AG39" s="15"/>
-      <c r="AH39" s="15"/>
-      <c r="AI39" s="15"/>
-      <c r="AJ39" s="15"/>
-      <c r="AK39" s="15"/>
-      <c r="AL39" s="15"/>
-      <c r="AM39" s="61"/>
+      <c r="AF39" s="153"/>
+      <c r="AG39" s="153"/>
+      <c r="AH39" s="153"/>
+      <c r="AI39" s="153"/>
+      <c r="AJ39" s="153"/>
+      <c r="AK39" s="153"/>
+      <c r="AL39" s="153"/>
+      <c r="AM39" s="60"/>
     </row>
     <row r="40" spans="1:41">
-      <c r="A40" s="60"/>
-      <c r="B40" s="27" t="s">
+      <c r="A40" s="59"/>
+      <c r="B40" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="28" t="s">
+      <c r="C40" s="135" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="28">
+      <c r="D40" s="135">
         <v>4</v>
       </c>
-      <c r="E40" s="28"/>
-      <c r="F40" s="91"/>
+      <c r="E40" s="135"/>
+      <c r="F40" s="87"/>
       <c r="G40" s="11"/>
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
@@ -3291,10 +3417,10 @@
       <c r="M40" s="11"/>
       <c r="N40" s="14"/>
       <c r="O40" s="11"/>
-      <c r="P40" s="118"/>
-      <c r="Q40" s="118"/>
-      <c r="R40" s="118"/>
-      <c r="S40" s="122"/>
+      <c r="P40" s="111"/>
+      <c r="Q40" s="111"/>
+      <c r="R40" s="111"/>
+      <c r="S40" s="114"/>
       <c r="T40" s="11"/>
       <c r="U40" s="14"/>
       <c r="V40" s="11"/>
@@ -3314,69 +3440,69 @@
       <c r="AJ40" s="15"/>
       <c r="AK40" s="15"/>
       <c r="AL40" s="15"/>
-      <c r="AM40" s="61"/>
-      <c r="AO40" s="103"/>
+      <c r="AM40" s="60"/>
+      <c r="AO40" s="98"/>
     </row>
     <row r="41" spans="1:41">
-      <c r="A41" s="60"/>
+      <c r="A41" s="59"/>
       <c r="B41" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="112" t="s">
+      <c r="C41" s="105" t="s">
         <v>55</v>
       </c>
       <c r="D41" s="28">
         <v>3</v>
       </c>
       <c r="E41" s="28"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="13"/>
-      <c r="M41" s="11"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="152"/>
+      <c r="H41" s="152"/>
+      <c r="I41" s="152"/>
+      <c r="J41" s="152"/>
+      <c r="K41" s="152"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="152"/>
       <c r="N41" s="14"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="106"/>
-      <c r="R41" s="106"/>
-      <c r="S41" s="106"/>
-      <c r="T41" s="11"/>
+      <c r="O41" s="152"/>
+      <c r="P41" s="152"/>
+      <c r="Q41" s="101"/>
+      <c r="R41" s="101"/>
+      <c r="S41" s="101"/>
+      <c r="T41" s="152"/>
       <c r="U41" s="14"/>
-      <c r="V41" s="11"/>
-      <c r="W41" s="11"/>
-      <c r="X41" s="11"/>
-      <c r="Y41" s="11"/>
-      <c r="Z41" s="15"/>
-      <c r="AA41" s="15"/>
-      <c r="AB41" s="15"/>
-      <c r="AC41" s="15"/>
-      <c r="AD41" s="15"/>
+      <c r="V41" s="152"/>
+      <c r="W41" s="152"/>
+      <c r="X41" s="152"/>
+      <c r="Y41" s="152"/>
+      <c r="Z41" s="153"/>
+      <c r="AA41" s="153"/>
+      <c r="AB41" s="153"/>
+      <c r="AC41" s="153"/>
+      <c r="AD41" s="153"/>
       <c r="AE41" s="16"/>
-      <c r="AF41" s="15"/>
-      <c r="AG41" s="15"/>
-      <c r="AH41" s="15"/>
-      <c r="AI41" s="15"/>
-      <c r="AJ41" s="15"/>
-      <c r="AK41" s="15"/>
-      <c r="AL41" s="15"/>
-      <c r="AM41" s="61"/>
+      <c r="AF41" s="153"/>
+      <c r="AG41" s="153"/>
+      <c r="AH41" s="153"/>
+      <c r="AI41" s="153"/>
+      <c r="AJ41" s="153"/>
+      <c r="AK41" s="153"/>
+      <c r="AL41" s="153"/>
+      <c r="AM41" s="60"/>
     </row>
     <row r="42" spans="1:41">
-      <c r="A42" s="60"/>
-      <c r="B42" s="27" t="s">
+      <c r="A42" s="59"/>
+      <c r="B42" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C42" s="135" t="s">
         <v>59</v>
       </c>
-      <c r="D42" s="28">
+      <c r="D42" s="135">
         <v>1</v>
       </c>
-      <c r="E42" s="28"/>
-      <c r="F42" s="91"/>
+      <c r="E42" s="135"/>
+      <c r="F42" s="87"/>
       <c r="G42" s="11"/>
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
@@ -3392,7 +3518,7 @@
       <c r="S42" s="11"/>
       <c r="T42" s="11"/>
       <c r="U42" s="14"/>
-      <c r="V42" s="106"/>
+      <c r="V42" s="101"/>
       <c r="W42" s="11"/>
       <c r="X42" s="11"/>
       <c r="Y42" s="11"/>
@@ -3409,10 +3535,10 @@
       <c r="AJ42" s="15"/>
       <c r="AK42" s="15"/>
       <c r="AL42" s="15"/>
-      <c r="AM42" s="61"/>
+      <c r="AM42" s="60"/>
     </row>
     <row r="43" spans="1:41">
-      <c r="A43" s="60"/>
+      <c r="A43" s="59"/>
       <c r="B43" s="27" t="s">
         <v>63</v>
       </c>
@@ -3423,144 +3549,144 @@
         <v>3</v>
       </c>
       <c r="E43" s="28"/>
-      <c r="F43" s="91"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="13"/>
-      <c r="M43" s="11"/>
+      <c r="F43" s="87"/>
+      <c r="G43" s="152"/>
+      <c r="H43" s="152"/>
+      <c r="I43" s="152"/>
+      <c r="J43" s="152"/>
+      <c r="K43" s="152"/>
+      <c r="L43" s="154"/>
+      <c r="M43" s="152"/>
       <c r="N43" s="14"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11"/>
-      <c r="R43" s="11"/>
-      <c r="S43" s="11"/>
-      <c r="T43" s="11"/>
+      <c r="O43" s="152"/>
+      <c r="P43" s="152"/>
+      <c r="Q43" s="152"/>
+      <c r="R43" s="152"/>
+      <c r="S43" s="152"/>
+      <c r="T43" s="152"/>
       <c r="U43" s="14"/>
-      <c r="V43" s="11"/>
-      <c r="W43" s="118"/>
-      <c r="X43" s="118"/>
-      <c r="Y43" s="118"/>
-      <c r="Z43" s="106"/>
-      <c r="AA43" s="106"/>
-      <c r="AB43" s="15"/>
-      <c r="AC43" s="15"/>
-      <c r="AD43" s="15"/>
+      <c r="V43" s="152"/>
+      <c r="W43" s="111"/>
+      <c r="X43" s="111"/>
+      <c r="Y43" s="111"/>
+      <c r="Z43" s="101"/>
+      <c r="AA43" s="101"/>
+      <c r="AB43" s="153"/>
+      <c r="AC43" s="153"/>
+      <c r="AD43" s="153"/>
       <c r="AE43" s="16"/>
-      <c r="AF43" s="15"/>
-      <c r="AG43" s="15"/>
-      <c r="AH43" s="15"/>
-      <c r="AI43" s="15"/>
-      <c r="AJ43" s="15"/>
-      <c r="AK43" s="15"/>
-      <c r="AL43" s="15"/>
-      <c r="AM43" s="61"/>
+      <c r="AF43" s="153"/>
+      <c r="AG43" s="153"/>
+      <c r="AH43" s="153"/>
+      <c r="AI43" s="153"/>
+      <c r="AJ43" s="153"/>
+      <c r="AK43" s="153"/>
+      <c r="AL43" s="153"/>
+      <c r="AM43" s="60"/>
     </row>
     <row r="44" spans="1:41">
-      <c r="A44" s="60"/>
+      <c r="A44" s="59"/>
       <c r="B44" s="31" t="s">
         <v>64</v>
       </c>
       <c r="C44" s="31"/>
       <c r="D44" s="31"/>
       <c r="E44" s="31"/>
-      <c r="F44" s="91"/>
-      <c r="G44" s="91"/>
-      <c r="H44" s="91"/>
-      <c r="I44" s="91"/>
-      <c r="J44" s="91"/>
-      <c r="K44" s="91"/>
-      <c r="L44" s="92"/>
-      <c r="M44" s="91"/>
+      <c r="F44" s="87"/>
+      <c r="G44" s="87"/>
+      <c r="H44" s="87"/>
+      <c r="I44" s="87"/>
+      <c r="J44" s="87"/>
+      <c r="K44" s="87"/>
+      <c r="L44" s="88"/>
+      <c r="M44" s="87"/>
       <c r="N44" s="23"/>
-      <c r="O44" s="91"/>
-      <c r="P44" s="91"/>
-      <c r="Q44" s="91"/>
-      <c r="R44" s="91"/>
-      <c r="S44" s="91"/>
-      <c r="T44" s="91"/>
+      <c r="O44" s="87"/>
+      <c r="P44" s="87"/>
+      <c r="Q44" s="87"/>
+      <c r="R44" s="87"/>
+      <c r="S44" s="87"/>
+      <c r="T44" s="87"/>
       <c r="U44" s="23"/>
-      <c r="V44" s="91"/>
-      <c r="W44" s="91"/>
-      <c r="X44" s="91"/>
-      <c r="Y44" s="91"/>
-      <c r="Z44" s="91"/>
-      <c r="AA44" s="91"/>
-      <c r="AB44" s="91"/>
-      <c r="AC44" s="91"/>
-      <c r="AD44" s="91"/>
+      <c r="V44" s="87"/>
+      <c r="W44" s="87"/>
+      <c r="X44" s="87"/>
+      <c r="Y44" s="87"/>
+      <c r="Z44" s="87"/>
+      <c r="AA44" s="87"/>
+      <c r="AB44" s="87"/>
+      <c r="AC44" s="87"/>
+      <c r="AD44" s="87"/>
       <c r="AE44" s="23"/>
-      <c r="AF44" s="91"/>
-      <c r="AG44" s="91"/>
-      <c r="AH44" s="91"/>
-      <c r="AI44" s="91"/>
-      <c r="AJ44" s="91"/>
-      <c r="AK44" s="91"/>
-      <c r="AL44" s="91"/>
-      <c r="AM44" s="61"/>
+      <c r="AF44" s="87"/>
+      <c r="AG44" s="87"/>
+      <c r="AH44" s="87"/>
+      <c r="AI44" s="87"/>
+      <c r="AJ44" s="87"/>
+      <c r="AK44" s="87"/>
+      <c r="AL44" s="87"/>
+      <c r="AM44" s="60"/>
     </row>
     <row r="45" spans="1:41">
-      <c r="A45" s="60"/>
+      <c r="A45" s="59"/>
       <c r="B45" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C45" s="113" t="s">
-        <v>25</v>
+      <c r="C45" s="106" t="s">
+        <v>28</v>
       </c>
       <c r="D45" s="33">
         <v>2</v>
       </c>
       <c r="E45" s="33"/>
-      <c r="F45" s="91"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="35"/>
-      <c r="M45" s="34"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="162"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="162"/>
+      <c r="K45" s="162"/>
+      <c r="L45" s="163"/>
+      <c r="M45" s="162"/>
       <c r="N45" s="36"/>
-      <c r="O45" s="34"/>
-      <c r="P45" s="34"/>
-      <c r="Q45" s="34"/>
-      <c r="R45" s="34"/>
-      <c r="S45" s="34"/>
-      <c r="T45" s="34"/>
+      <c r="O45" s="162"/>
+      <c r="P45" s="162"/>
+      <c r="Q45" s="162"/>
+      <c r="R45" s="162"/>
+      <c r="S45" s="162"/>
+      <c r="T45" s="162"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="34"/>
-      <c r="W45" s="34"/>
-      <c r="X45" s="34"/>
-      <c r="Y45" s="34"/>
-      <c r="Z45" s="37"/>
-      <c r="AA45" s="111"/>
-      <c r="AB45" s="37"/>
-      <c r="AC45" s="105"/>
-      <c r="AD45" s="105"/>
+      <c r="V45" s="162"/>
+      <c r="W45" s="162"/>
+      <c r="X45" s="162"/>
+      <c r="Y45" s="162"/>
+      <c r="Z45" s="164"/>
+      <c r="AA45" s="165"/>
+      <c r="AB45" s="164"/>
+      <c r="AC45" s="100"/>
+      <c r="AD45" s="100"/>
       <c r="AE45" s="23"/>
-      <c r="AF45" s="37"/>
-      <c r="AG45" s="37"/>
-      <c r="AH45" s="37"/>
-      <c r="AI45" s="37"/>
-      <c r="AJ45" s="37"/>
-      <c r="AK45" s="37"/>
-      <c r="AL45" s="37"/>
-      <c r="AM45" s="61"/>
+      <c r="AF45" s="164"/>
+      <c r="AG45" s="164"/>
+      <c r="AH45" s="164"/>
+      <c r="AI45" s="164"/>
+      <c r="AJ45" s="164"/>
+      <c r="AK45" s="164"/>
+      <c r="AL45" s="164"/>
+      <c r="AM45" s="60"/>
     </row>
     <row r="46" spans="1:41">
-      <c r="A46" s="60"/>
-      <c r="B46" s="94" t="s">
+      <c r="A46" s="59"/>
+      <c r="B46" s="136" t="s">
         <v>66</v>
       </c>
-      <c r="C46" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" s="33">
+      <c r="C46" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="100">
         <v>2</v>
       </c>
-      <c r="E46" s="33"/>
-      <c r="F46" s="91"/>
+      <c r="E46" s="100"/>
+      <c r="F46" s="87"/>
       <c r="G46" s="34"/>
       <c r="H46" s="34"/>
       <c r="I46" s="34"/>
@@ -3583,8 +3709,8 @@
       <c r="Z46" s="37"/>
       <c r="AA46" s="37"/>
       <c r="AB46" s="37"/>
-      <c r="AC46" s="105"/>
-      <c r="AD46" s="105"/>
+      <c r="AC46" s="100"/>
+      <c r="AD46" s="100"/>
       <c r="AE46" s="23"/>
       <c r="AF46" s="37"/>
       <c r="AG46" s="37"/>
@@ -3593,10 +3719,10 @@
       <c r="AJ46" s="37"/>
       <c r="AK46" s="37"/>
       <c r="AL46" s="37"/>
-      <c r="AM46" s="61"/>
+      <c r="AM46" s="60"/>
     </row>
     <row r="47" spans="1:41">
-      <c r="A47" s="60"/>
+      <c r="A47" s="59"/>
       <c r="B47" s="32" t="s">
         <v>67</v>
       </c>
@@ -3607,54 +3733,54 @@
         <v>2</v>
       </c>
       <c r="E47" s="33"/>
-      <c r="F47" s="91"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="34"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="35"/>
-      <c r="M47" s="34"/>
+      <c r="F47" s="87"/>
+      <c r="G47" s="162"/>
+      <c r="H47" s="162"/>
+      <c r="I47" s="162"/>
+      <c r="J47" s="162"/>
+      <c r="K47" s="162"/>
+      <c r="L47" s="163"/>
+      <c r="M47" s="162"/>
       <c r="N47" s="36"/>
-      <c r="O47" s="34"/>
-      <c r="P47" s="34"/>
-      <c r="Q47" s="34"/>
-      <c r="R47" s="34"/>
-      <c r="S47" s="34"/>
-      <c r="T47" s="34"/>
+      <c r="O47" s="162"/>
+      <c r="P47" s="162"/>
+      <c r="Q47" s="162"/>
+      <c r="R47" s="162"/>
+      <c r="S47" s="162"/>
+      <c r="T47" s="162"/>
       <c r="U47" s="36"/>
-      <c r="V47" s="34"/>
-      <c r="W47" s="34"/>
-      <c r="X47" s="34"/>
-      <c r="Y47" s="34"/>
-      <c r="Z47" s="37"/>
-      <c r="AA47" s="37"/>
-      <c r="AB47" s="37"/>
-      <c r="AC47" s="105"/>
-      <c r="AD47" s="105"/>
+      <c r="V47" s="162"/>
+      <c r="W47" s="162"/>
+      <c r="X47" s="162"/>
+      <c r="Y47" s="162"/>
+      <c r="Z47" s="164"/>
+      <c r="AA47" s="164"/>
+      <c r="AB47" s="164"/>
+      <c r="AC47" s="100"/>
+      <c r="AD47" s="100"/>
       <c r="AE47" s="23"/>
-      <c r="AF47" s="37"/>
-      <c r="AG47" s="37"/>
-      <c r="AH47" s="37"/>
-      <c r="AI47" s="37"/>
-      <c r="AJ47" s="37"/>
-      <c r="AK47" s="37"/>
-      <c r="AL47" s="37"/>
-      <c r="AM47" s="61"/>
+      <c r="AF47" s="164"/>
+      <c r="AG47" s="164"/>
+      <c r="AH47" s="164"/>
+      <c r="AI47" s="164"/>
+      <c r="AJ47" s="164"/>
+      <c r="AK47" s="164"/>
+      <c r="AL47" s="164"/>
+      <c r="AM47" s="60"/>
     </row>
     <row r="48" spans="1:41">
-      <c r="A48" s="60"/>
-      <c r="B48" s="32" t="s">
+      <c r="A48" s="59"/>
+      <c r="B48" s="137" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="33" t="s">
+      <c r="C48" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="33">
+      <c r="D48" s="100">
         <v>2</v>
       </c>
-      <c r="E48" s="33"/>
-      <c r="F48" s="91"/>
+      <c r="E48" s="100"/>
+      <c r="F48" s="87"/>
       <c r="G48" s="34"/>
       <c r="H48" s="34"/>
       <c r="I48" s="34"/>
@@ -3680,17 +3806,17 @@
       <c r="AC48" s="37"/>
       <c r="AD48" s="37"/>
       <c r="AE48" s="23"/>
-      <c r="AF48" s="104"/>
-      <c r="AG48" s="104"/>
+      <c r="AF48" s="99"/>
+      <c r="AG48" s="99"/>
       <c r="AH48" s="37"/>
       <c r="AI48" s="37"/>
       <c r="AJ48" s="37"/>
       <c r="AK48" s="37"/>
       <c r="AL48" s="37"/>
-      <c r="AM48" s="61"/>
+      <c r="AM48" s="60"/>
     </row>
     <row r="49" spans="1:39">
-      <c r="A49" s="60"/>
+      <c r="A49" s="59"/>
       <c r="B49" s="32" t="s">
         <v>69</v>
       </c>
@@ -3701,148 +3827,148 @@
         <v>2</v>
       </c>
       <c r="E49" s="33"/>
-      <c r="F49" s="91"/>
-      <c r="G49" s="34"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-      <c r="J49" s="34"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="35"/>
-      <c r="M49" s="34"/>
+      <c r="F49" s="87"/>
+      <c r="G49" s="162"/>
+      <c r="H49" s="162"/>
+      <c r="I49" s="162"/>
+      <c r="J49" s="162"/>
+      <c r="K49" s="162"/>
+      <c r="L49" s="163"/>
+      <c r="M49" s="162"/>
       <c r="N49" s="36"/>
-      <c r="O49" s="34"/>
-      <c r="P49" s="34"/>
-      <c r="Q49" s="34"/>
-      <c r="R49" s="34"/>
-      <c r="S49" s="34"/>
-      <c r="T49" s="34"/>
+      <c r="O49" s="162"/>
+      <c r="P49" s="162"/>
+      <c r="Q49" s="162"/>
+      <c r="R49" s="162"/>
+      <c r="S49" s="162"/>
+      <c r="T49" s="162"/>
       <c r="U49" s="36"/>
-      <c r="V49" s="34"/>
-      <c r="W49" s="34"/>
-      <c r="X49" s="34"/>
-      <c r="Y49" s="34"/>
-      <c r="Z49" s="37"/>
-      <c r="AA49" s="37"/>
-      <c r="AB49" s="37"/>
-      <c r="AC49" s="37"/>
-      <c r="AD49" s="37"/>
+      <c r="V49" s="162"/>
+      <c r="W49" s="162"/>
+      <c r="X49" s="162"/>
+      <c r="Y49" s="162"/>
+      <c r="Z49" s="164"/>
+      <c r="AA49" s="164"/>
+      <c r="AB49" s="164"/>
+      <c r="AC49" s="164"/>
+      <c r="AD49" s="164"/>
       <c r="AE49" s="23"/>
-      <c r="AF49" s="38"/>
-      <c r="AG49" s="38"/>
+      <c r="AF49" s="166"/>
+      <c r="AG49" s="166"/>
       <c r="AH49" s="39"/>
       <c r="AI49" s="39"/>
       <c r="AJ49" s="38"/>
       <c r="AK49" s="38"/>
       <c r="AL49" s="38"/>
-      <c r="AM49" s="61"/>
+      <c r="AM49" s="60"/>
     </row>
     <row r="50" spans="1:39">
-      <c r="A50" s="60"/>
-      <c r="B50" s="32" t="s">
+      <c r="A50" s="59"/>
+      <c r="B50" s="137" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="113" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" s="33">
+      <c r="C50" s="138" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="100">
         <v>2</v>
       </c>
-      <c r="E50" s="33"/>
-      <c r="F50" s="129"/>
-      <c r="G50" s="130"/>
-      <c r="H50" s="130"/>
-      <c r="I50" s="130"/>
-      <c r="J50" s="130"/>
-      <c r="K50" s="130"/>
-      <c r="L50" s="131"/>
-      <c r="M50" s="130"/>
-      <c r="N50" s="132"/>
-      <c r="O50" s="130"/>
-      <c r="P50" s="130"/>
-      <c r="Q50" s="130"/>
-      <c r="R50" s="130"/>
-      <c r="S50" s="130"/>
-      <c r="T50" s="130"/>
-      <c r="U50" s="132"/>
-      <c r="V50" s="130"/>
-      <c r="W50" s="130"/>
-      <c r="X50" s="130"/>
-      <c r="Y50" s="130"/>
-      <c r="Z50" s="133"/>
-      <c r="AA50" s="133"/>
-      <c r="AB50" s="133"/>
-      <c r="AC50" s="133"/>
-      <c r="AD50" s="133"/>
-      <c r="AE50" s="134"/>
-      <c r="AF50" s="135"/>
-      <c r="AG50" s="135"/>
-      <c r="AH50" s="125"/>
-      <c r="AI50" s="126"/>
-      <c r="AJ50" s="136"/>
-      <c r="AK50" s="136"/>
-      <c r="AL50" s="136"/>
-      <c r="AM50" s="61"/>
+      <c r="E50" s="100"/>
+      <c r="F50" s="120"/>
+      <c r="G50" s="121"/>
+      <c r="H50" s="121"/>
+      <c r="I50" s="121"/>
+      <c r="J50" s="121"/>
+      <c r="K50" s="121"/>
+      <c r="L50" s="122"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="123"/>
+      <c r="O50" s="121"/>
+      <c r="P50" s="121"/>
+      <c r="Q50" s="121"/>
+      <c r="R50" s="121"/>
+      <c r="S50" s="121"/>
+      <c r="T50" s="121"/>
+      <c r="U50" s="123"/>
+      <c r="V50" s="121"/>
+      <c r="W50" s="121"/>
+      <c r="X50" s="121"/>
+      <c r="Y50" s="121"/>
+      <c r="Z50" s="124"/>
+      <c r="AA50" s="124"/>
+      <c r="AB50" s="124"/>
+      <c r="AC50" s="124"/>
+      <c r="AD50" s="124"/>
+      <c r="AE50" s="125"/>
+      <c r="AF50" s="126"/>
+      <c r="AG50" s="126"/>
+      <c r="AH50" s="116"/>
+      <c r="AI50" s="117"/>
+      <c r="AJ50" s="127"/>
+      <c r="AK50" s="127"/>
+      <c r="AL50" s="127"/>
+      <c r="AM50" s="60"/>
     </row>
     <row r="51" spans="1:39">
-      <c r="A51" s="60"/>
-      <c r="B51" s="94" t="s">
+      <c r="A51" s="59"/>
+      <c r="B51" s="89" t="s">
         <v>71</v>
       </c>
       <c r="C51" s="33" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D51" s="33">
         <v>2</v>
       </c>
       <c r="E51" s="33"/>
-      <c r="F51" s="91"/>
-      <c r="G51" s="34"/>
-      <c r="H51" s="34"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="34"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="35"/>
-      <c r="M51" s="34"/>
+      <c r="F51" s="87"/>
+      <c r="G51" s="162"/>
+      <c r="H51" s="162"/>
+      <c r="I51" s="162"/>
+      <c r="J51" s="162"/>
+      <c r="K51" s="162"/>
+      <c r="L51" s="163"/>
+      <c r="M51" s="162"/>
       <c r="N51" s="36"/>
-      <c r="O51" s="34"/>
-      <c r="P51" s="34"/>
-      <c r="Q51" s="34"/>
-      <c r="R51" s="34"/>
-      <c r="S51" s="34"/>
-      <c r="T51" s="34"/>
+      <c r="O51" s="162"/>
+      <c r="P51" s="162"/>
+      <c r="Q51" s="162"/>
+      <c r="R51" s="162"/>
+      <c r="S51" s="162"/>
+      <c r="T51" s="162"/>
       <c r="U51" s="36"/>
-      <c r="V51" s="34"/>
-      <c r="W51" s="34"/>
-      <c r="X51" s="34"/>
-      <c r="Y51" s="34"/>
-      <c r="Z51" s="37"/>
-      <c r="AA51" s="37"/>
-      <c r="AB51" s="37"/>
-      <c r="AC51" s="37"/>
-      <c r="AD51" s="37"/>
+      <c r="V51" s="162"/>
+      <c r="W51" s="162"/>
+      <c r="X51" s="162"/>
+      <c r="Y51" s="162"/>
+      <c r="Z51" s="164"/>
+      <c r="AA51" s="164"/>
+      <c r="AB51" s="164"/>
+      <c r="AC51" s="164"/>
+      <c r="AD51" s="164"/>
       <c r="AE51" s="23"/>
-      <c r="AF51" s="38"/>
-      <c r="AG51" s="38"/>
-      <c r="AH51" s="127"/>
-      <c r="AI51" s="128"/>
+      <c r="AF51" s="166"/>
+      <c r="AG51" s="166"/>
+      <c r="AH51" s="158"/>
+      <c r="AI51" s="159"/>
       <c r="AJ51" s="39"/>
       <c r="AK51" s="39"/>
       <c r="AL51" s="39"/>
-      <c r="AM51" s="61"/>
+      <c r="AM51" s="60"/>
     </row>
     <row r="52" spans="1:39">
-      <c r="A52" s="60"/>
-      <c r="B52" s="32" t="s">
+      <c r="A52" s="59"/>
+      <c r="B52" s="137" t="s">
         <v>72</v>
       </c>
-      <c r="C52" s="33" t="s">
+      <c r="C52" s="100" t="s">
         <v>34</v>
       </c>
-      <c r="D52" s="33">
+      <c r="D52" s="100">
         <v>2</v>
       </c>
-      <c r="E52" s="33"/>
-      <c r="F52" s="91"/>
+      <c r="E52" s="100"/>
+      <c r="F52" s="87"/>
       <c r="G52" s="34"/>
       <c r="H52" s="34"/>
       <c r="I52" s="34"/>
@@ -3870,15 +3996,15 @@
       <c r="AE52" s="23"/>
       <c r="AF52" s="38"/>
       <c r="AG52" s="38"/>
-      <c r="AH52" s="127"/>
-      <c r="AI52" s="128"/>
+      <c r="AH52" s="118"/>
+      <c r="AI52" s="119"/>
       <c r="AJ52" s="39"/>
       <c r="AK52" s="39"/>
       <c r="AL52" s="39"/>
-      <c r="AM52" s="61"/>
+      <c r="AM52" s="60"/>
     </row>
     <row r="53" spans="1:39">
-      <c r="A53" s="60"/>
+      <c r="A53" s="59"/>
       <c r="B53" s="32" t="s">
         <v>68</v>
       </c>
@@ -3889,80 +4015,80 @@
         <v>2</v>
       </c>
       <c r="E53" s="33"/>
-      <c r="F53" s="91"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="34"/>
-      <c r="I53" s="34"/>
-      <c r="J53" s="34"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="35"/>
-      <c r="M53" s="34"/>
+      <c r="F53" s="87"/>
+      <c r="G53" s="162"/>
+      <c r="H53" s="162"/>
+      <c r="I53" s="162"/>
+      <c r="J53" s="162"/>
+      <c r="K53" s="162"/>
+      <c r="L53" s="163"/>
+      <c r="M53" s="162"/>
       <c r="N53" s="36"/>
-      <c r="O53" s="34"/>
-      <c r="P53" s="34"/>
-      <c r="Q53" s="34"/>
-      <c r="R53" s="34"/>
-      <c r="S53" s="34"/>
-      <c r="T53" s="34"/>
+      <c r="O53" s="162"/>
+      <c r="P53" s="162"/>
+      <c r="Q53" s="162"/>
+      <c r="R53" s="162"/>
+      <c r="S53" s="162"/>
+      <c r="T53" s="162"/>
       <c r="U53" s="36"/>
-      <c r="V53" s="34"/>
-      <c r="W53" s="34"/>
-      <c r="X53" s="34"/>
-      <c r="Y53" s="34"/>
-      <c r="Z53" s="37"/>
-      <c r="AA53" s="37"/>
-      <c r="AB53" s="37"/>
-      <c r="AC53" s="37"/>
-      <c r="AD53" s="37"/>
+      <c r="V53" s="162"/>
+      <c r="W53" s="162"/>
+      <c r="X53" s="162"/>
+      <c r="Y53" s="162"/>
+      <c r="Z53" s="164"/>
+      <c r="AA53" s="164"/>
+      <c r="AB53" s="164"/>
+      <c r="AC53" s="164"/>
+      <c r="AD53" s="164"/>
       <c r="AE53" s="23"/>
-      <c r="AF53" s="38"/>
-      <c r="AG53" s="38"/>
-      <c r="AH53" s="127"/>
-      <c r="AI53" s="128"/>
+      <c r="AF53" s="166"/>
+      <c r="AG53" s="166"/>
+      <c r="AH53" s="158"/>
+      <c r="AI53" s="159"/>
       <c r="AJ53" s="39"/>
       <c r="AK53" s="39"/>
       <c r="AL53" s="39"/>
-      <c r="AM53" s="61"/>
+      <c r="AM53" s="60"/>
     </row>
     <row r="54" spans="1:39">
       <c r="A54" s="3"/>
-      <c r="B54" s="85"/>
-      <c r="C54" s="85"/>
-      <c r="D54" s="85"/>
-      <c r="E54" s="85"/>
-      <c r="F54" s="85"/>
-      <c r="G54" s="86"/>
-      <c r="H54" s="86"/>
-      <c r="I54" s="86"/>
-      <c r="J54" s="86"/>
-      <c r="K54" s="86"/>
-      <c r="L54" s="86"/>
-      <c r="M54" s="86"/>
-      <c r="N54" s="86"/>
-      <c r="O54" s="86"/>
-      <c r="P54" s="86"/>
-      <c r="Q54" s="86"/>
-      <c r="R54" s="86"/>
-      <c r="S54" s="86"/>
-      <c r="T54" s="86"/>
-      <c r="U54" s="86"/>
-      <c r="V54" s="86"/>
-      <c r="W54" s="86"/>
-      <c r="X54" s="86"/>
-      <c r="Y54" s="86"/>
-      <c r="Z54" s="85"/>
-      <c r="AA54" s="85"/>
-      <c r="AB54" s="85"/>
-      <c r="AC54" s="85"/>
-      <c r="AD54" s="85"/>
-      <c r="AE54" s="85"/>
-      <c r="AF54" s="85"/>
-      <c r="AG54" s="85"/>
-      <c r="AH54" s="85"/>
-      <c r="AI54" s="85"/>
-      <c r="AJ54" s="85"/>
-      <c r="AK54" s="85"/>
-      <c r="AL54" s="85"/>
+      <c r="B54" s="82"/>
+      <c r="C54" s="82"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="82"/>
+      <c r="F54" s="82"/>
+      <c r="G54" s="83"/>
+      <c r="H54" s="83"/>
+      <c r="I54" s="83"/>
+      <c r="J54" s="83"/>
+      <c r="K54" s="83"/>
+      <c r="L54" s="83"/>
+      <c r="M54" s="83"/>
+      <c r="N54" s="83"/>
+      <c r="O54" s="83"/>
+      <c r="P54" s="83"/>
+      <c r="Q54" s="83"/>
+      <c r="R54" s="83"/>
+      <c r="S54" s="83"/>
+      <c r="T54" s="83"/>
+      <c r="U54" s="83"/>
+      <c r="V54" s="83"/>
+      <c r="W54" s="83"/>
+      <c r="X54" s="83"/>
+      <c r="Y54" s="83"/>
+      <c r="Z54" s="82"/>
+      <c r="AA54" s="82"/>
+      <c r="AB54" s="82"/>
+      <c r="AC54" s="82"/>
+      <c r="AD54" s="82"/>
+      <c r="AE54" s="82"/>
+      <c r="AF54" s="82"/>
+      <c r="AG54" s="82"/>
+      <c r="AH54" s="82"/>
+      <c r="AI54" s="82"/>
+      <c r="AJ54" s="82"/>
+      <c r="AK54" s="82"/>
+      <c r="AL54" s="82"/>
       <c r="AM54" s="2"/>
     </row>
   </sheetData>
